--- a/kurs-analiz-akcij/Трекер обучения анализу акций.xlsx
+++ b/kurs-analiz-akcij/Трекер обучения анализу акций.xlsx
@@ -381,6 +381,288 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Прогресс по уровням, %</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!E30</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$A$31:$A$43</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$E$31:$E$43</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Выполнено</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Уровень</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Часы обучения по уровням</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!G30</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$A$31:$A$43</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$G$31:$G$43</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Уровень</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Часы</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Статусы этапов программы</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$A$8:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$B$8:$B$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+          <showPercent val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -496,6 +778,77 @@
     </comment>
   </commentList>
 </comments>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -797,6 +1150,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
@@ -1324,6 +1678,11 @@
           <t>Средний балл</t>
         </is>
       </c>
+      <c r="G30" s="19" t="inlineStr">
+        <is>
+          <t>Часов</t>
+        </is>
+      </c>
       <c r="H30" s="7">
         <f>IF($H29="","",$H29-1)</f>
         <v/>
@@ -1358,6 +1717,10 @@
         <f>IFERROR(AVERAGEIF(Roadmap!$B$3:$B$200,$A31,Roadmap!$P$3:$P$200),0)</f>
         <v/>
       </c>
+      <c r="G31" s="13">
+        <f>SUMIF(Roadmap!$B$3:$B$200,$A31,Roadmap!$Q$3:$Q$200)</f>
+        <v/>
+      </c>
       <c r="H31" s="7">
         <f>IF($H30="","",$H30-1)</f>
         <v/>
@@ -1392,6 +1755,10 @@
         <f>IFERROR(AVERAGEIF(Roadmap!$B$3:$B$200,$A32,Roadmap!$P$3:$P$200),0)</f>
         <v/>
       </c>
+      <c r="G32" s="13">
+        <f>SUMIF(Roadmap!$B$3:$B$200,$A32,Roadmap!$Q$3:$Q$200)</f>
+        <v/>
+      </c>
       <c r="H32" s="7">
         <f>IF($H31="","",$H31-1)</f>
         <v/>
@@ -1426,6 +1793,10 @@
         <f>IFERROR(AVERAGEIF(Roadmap!$B$3:$B$200,$A33,Roadmap!$P$3:$P$200),0)</f>
         <v/>
       </c>
+      <c r="G33" s="13">
+        <f>SUMIF(Roadmap!$B$3:$B$200,$A33,Roadmap!$Q$3:$Q$200)</f>
+        <v/>
+      </c>
       <c r="H33" s="7">
         <f>IF($H32="","",$H32-1)</f>
         <v/>
@@ -1460,6 +1831,10 @@
         <f>IFERROR(AVERAGEIF(Roadmap!$B$3:$B$200,$A34,Roadmap!$P$3:$P$200),0)</f>
         <v/>
       </c>
+      <c r="G34" s="13">
+        <f>SUMIF(Roadmap!$B$3:$B$200,$A34,Roadmap!$Q$3:$Q$200)</f>
+        <v/>
+      </c>
       <c r="H34" s="7">
         <f>IF($H33="","",$H33-1)</f>
         <v/>
@@ -1494,6 +1869,10 @@
         <f>IFERROR(AVERAGEIF(Roadmap!$B$3:$B$200,$A35,Roadmap!$P$3:$P$200),0)</f>
         <v/>
       </c>
+      <c r="G35" s="13">
+        <f>SUMIF(Roadmap!$B$3:$B$200,$A35,Roadmap!$Q$3:$Q$200)</f>
+        <v/>
+      </c>
       <c r="H35" s="7">
         <f>IF($H34="","",$H34-1)</f>
         <v/>
@@ -1528,6 +1907,10 @@
         <f>IFERROR(AVERAGEIF(Roadmap!$B$3:$B$200,$A36,Roadmap!$P$3:$P$200),0)</f>
         <v/>
       </c>
+      <c r="G36" s="13">
+        <f>SUMIF(Roadmap!$B$3:$B$200,$A36,Roadmap!$Q$3:$Q$200)</f>
+        <v/>
+      </c>
       <c r="H36" s="7">
         <f>IF($H35="","",$H35-1)</f>
         <v/>
@@ -1562,6 +1945,10 @@
         <f>IFERROR(AVERAGEIF(Roadmap!$B$3:$B$200,$A37,Roadmap!$P$3:$P$200),0)</f>
         <v/>
       </c>
+      <c r="G37" s="13">
+        <f>SUMIF(Roadmap!$B$3:$B$200,$A37,Roadmap!$Q$3:$Q$200)</f>
+        <v/>
+      </c>
       <c r="H37" s="7">
         <f>IF($H36="","",$H36-1)</f>
         <v/>
@@ -1596,6 +1983,10 @@
         <f>IFERROR(AVERAGEIF(Roadmap!$B$3:$B$200,$A38,Roadmap!$P$3:$P$200),0)</f>
         <v/>
       </c>
+      <c r="G38" s="13">
+        <f>SUMIF(Roadmap!$B$3:$B$200,$A38,Roadmap!$Q$3:$Q$200)</f>
+        <v/>
+      </c>
       <c r="H38" s="7">
         <f>IF($H37="","",$H37-1)</f>
         <v/>
@@ -1630,6 +2021,10 @@
         <f>IFERROR(AVERAGEIF(Roadmap!$B$3:$B$200,$A39,Roadmap!$P$3:$P$200),0)</f>
         <v/>
       </c>
+      <c r="G39" s="13">
+        <f>SUMIF(Roadmap!$B$3:$B$200,$A39,Roadmap!$Q$3:$Q$200)</f>
+        <v/>
+      </c>
       <c r="H39" s="7">
         <f>IF($H38="","",$H38-1)</f>
         <v/>
@@ -1664,6 +2059,10 @@
         <f>IFERROR(AVERAGEIF(Roadmap!$B$3:$B$200,$A40,Roadmap!$P$3:$P$200),0)</f>
         <v/>
       </c>
+      <c r="G40" s="13">
+        <f>SUMIF(Roadmap!$B$3:$B$200,$A40,Roadmap!$Q$3:$Q$200)</f>
+        <v/>
+      </c>
       <c r="H40" s="7">
         <f>IF($H39="","",$H39-1)</f>
         <v/>
@@ -1698,6 +2097,10 @@
         <f>IFERROR(AVERAGEIF(Roadmap!$B$3:$B$200,$A41,Roadmap!$P$3:$P$200),0)</f>
         <v/>
       </c>
+      <c r="G41" s="13">
+        <f>SUMIF(Roadmap!$B$3:$B$200,$A41,Roadmap!$Q$3:$Q$200)</f>
+        <v/>
+      </c>
       <c r="H41" s="7">
         <f>IF($H40="","",$H40-1)</f>
         <v/>
@@ -1732,6 +2135,10 @@
         <f>IFERROR(AVERAGEIF(Roadmap!$B$3:$B$200,$A42,Roadmap!$P$3:$P$200),0)</f>
         <v/>
       </c>
+      <c r="G42" s="13">
+        <f>SUMIF(Roadmap!$B$3:$B$200,$A42,Roadmap!$Q$3:$Q$200)</f>
+        <v/>
+      </c>
       <c r="H42" s="7">
         <f>IF($H41="","",$H41-1)</f>
         <v/>
@@ -1764,6 +2171,10 @@
       </c>
       <c r="F43" s="13">
         <f>IFERROR(AVERAGEIF(Roadmap!$B$3:$B$200,$A43,Roadmap!$P$3:$P$200),0)</f>
+        <v/>
+      </c>
+      <c r="G43" s="13">
+        <f>SUMIF(Roadmap!$B$3:$B$200,$A43,Roadmap!$Q$3:$Q$200)</f>
         <v/>
       </c>
       <c r="H43" s="7">
@@ -2048,6 +2459,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
